--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484756_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484756_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.0783</v>
+        <v>8.8863</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7696</v>
+        <v>4.4718</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3087</v>
+        <v>4.4146</v>
       </c>
       <c r="G2" t="n">
         <v>4.1992</v>
@@ -610,13 +610,13 @@
         <v>4.5288</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3286</v>
+        <v>0.4794</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0065</v>
+        <v>0.6956</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3221</v>
+        <v>-0.2163</v>
       </c>
       <c r="V2" t="n">
         <v>1.566</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.1483</v>
+        <v>6.0252</v>
       </c>
       <c r="E3" t="n">
-        <v>2.837</v>
+        <v>2.37</v>
       </c>
       <c r="F3" t="n">
-        <v>3.3113</v>
+        <v>3.6552</v>
       </c>
       <c r="G3" t="n">
         <v>3.1118</v>
@@ -688,13 +688,13 @@
         <v>3.5853</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0363</v>
+        <v>0.9132</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9028</v>
+        <v>0.4358</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1335</v>
+        <v>0.4774</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6415999999999999</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.8807</v>
+        <v>5.3046</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8106</v>
+        <v>0.8694</v>
       </c>
       <c r="F4" t="n">
-        <v>5.0701</v>
+        <v>4.4352</v>
       </c>
       <c r="G4" t="n">
         <v>0.08649999999999999</v>
@@ -766,13 +766,13 @@
         <v>3.9627</v>
       </c>
       <c r="S4" t="n">
-        <v>1.8506</v>
+        <v>1.2744</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7729</v>
+        <v>0.8317</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0776</v>
+        <v>0.4427</v>
       </c>
       <c r="V4" t="n">
         <v>0.9244</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. BOSCH ROIG</t>
+          <t>J. DALMAU ROIG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3185</v>
+        <v>2.6567</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.101</v>
+        <v>0.1336</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4195</v>
+        <v>2.5231</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5899</v>
+        <v>-0.1442</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.5855</v>
+        <v>1.4885</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9956</v>
+        <v>-1.6327</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.3884</v>
+        <v>0.2902</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.1457</v>
+        <v>2.1396</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7574</v>
+        <v>-1.8494</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2015</v>
+        <v>-0.4344</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4398</v>
+        <v>-0.6511</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2383</v>
+        <v>0.2167</v>
       </c>
       <c r="P5" t="n">
-        <v>3.0192</v>
+        <v>1.887</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R5" t="n">
-        <v>3.0192</v>
+        <v>2.8305</v>
       </c>
       <c r="S5" t="n">
-        <v>0.191</v>
+        <v>0.9139</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2874</v>
+        <v>0.7869</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0964</v>
+        <v>0.127</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. VERDEGUER FERRER</t>
+          <t>J. BOSCH ROIG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4554</v>
+        <v>2.3857</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3755</v>
+        <v>-0.1396</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0799</v>
+        <v>2.5253</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.6692</v>
+        <v>-0.5899</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.031</v>
+        <v>-1.5855</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3618</v>
+        <v>0.9956</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0929</v>
+        <v>-0.3884</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.7709</v>
+        <v>-1.1457</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8637</v>
+        <v>0.7574</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.762</v>
+        <v>-0.2015</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.2601</v>
+        <v>-0.4398</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4981</v>
+        <v>0.2383</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6983</v>
+        <v>3.0192</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>3.5853</v>
+        <v>3.0192</v>
       </c>
       <c r="S6" t="n">
-        <v>2.0868</v>
+        <v>0.2582</v>
       </c>
       <c r="T6" t="n">
-        <v>1.6605</v>
+        <v>0.2487</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4263</v>
+        <v>0.0094</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6606</v>
+        <v>-0.3018</v>
       </c>
       <c r="W6" t="n">
-        <v>1.5091</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.1696</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. DALMAU ROIG</t>
+          <t>M. RODILLA ALCAIDE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4506</v>
+        <v>0.8596</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8609</v>
+        <v>-0.2159</v>
       </c>
       <c r="F7" t="n">
-        <v>2.3115</v>
+        <v>1.0755</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1442</v>
+        <v>0.1624</v>
       </c>
       <c r="H7" t="n">
-        <v>1.4885</v>
+        <v>1.2193</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.6327</v>
+        <v>-1.0569</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2902</v>
+        <v>0.8238</v>
       </c>
       <c r="K7" t="n">
-        <v>2.1396</v>
+        <v>1.4478</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.8494</v>
+        <v>-0.624</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4344</v>
+        <v>-0.6614</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6511</v>
+        <v>-0.2285</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2167</v>
+        <v>-0.4329</v>
       </c>
       <c r="P7" t="n">
-        <v>1.887</v>
+        <v>0.5661</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9435</v>
       </c>
       <c r="R7" t="n">
-        <v>2.8305</v>
+        <v>1.5096</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2922</v>
+        <v>0.4329</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2076</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.08459999999999999</v>
+        <v>0.5291</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. MARTIN FERNANDEZ</t>
+          <t>L. VERDEGUER FERRER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1799</v>
+        <v>0.4193</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3463</v>
+        <v>0.5775</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1663</v>
+        <v>-0.1582</v>
       </c>
       <c r="G8" t="n">
-        <v>2.8479</v>
+        <v>-1.6692</v>
       </c>
       <c r="H8" t="n">
-        <v>1.5879</v>
+        <v>-3.031</v>
       </c>
       <c r="I8" t="n">
-        <v>1.26</v>
+        <v>1.3618</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7601</v>
+        <v>0.0929</v>
       </c>
       <c r="K8" t="n">
-        <v>1.0197</v>
+        <v>-0.7709</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7403</v>
+        <v>0.8637</v>
       </c>
       <c r="M8" t="n">
-        <v>1.0878</v>
+        <v>-1.762</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5682</v>
+        <v>-2.2601</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5196</v>
+        <v>0.4981</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9435</v>
+        <v>1.6983</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.887</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9435</v>
+        <v>3.5853</v>
       </c>
       <c r="S8" t="n">
-        <v>0.766</v>
+        <v>1.0507</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4732</v>
+        <v>0.8626</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2928</v>
+        <v>0.1882</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.4904</v>
+        <v>-0.6606</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.5091</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.4904</v>
+        <v>-2.1696</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. RODILLA ALCAIDE</t>
+          <t>J. MARTIN FERNANDEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1012</v>
+        <v>0.127</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8593</v>
+        <v>0.3463</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7581</v>
+        <v>-0.2192</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1624</v>
+        <v>2.8479</v>
       </c>
       <c r="H9" t="n">
-        <v>1.2193</v>
+        <v>1.5879</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0569</v>
+        <v>1.26</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8238</v>
+        <v>1.7601</v>
       </c>
       <c r="K9" t="n">
-        <v>1.4478</v>
+        <v>1.0197</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.624</v>
+        <v>0.7403</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6614</v>
+        <v>1.0878</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2285</v>
+        <v>0.5682</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4329</v>
+        <v>0.5196</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5661</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5096</v>
+        <v>0.9435</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5279</v>
+        <v>0.7131</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7396</v>
+        <v>0.4732</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2116</v>
+        <v>0.2399</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3018</v>
+        <v>-2.4904</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.3018</v>
+        <v>-2.4904</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V. PELUFO LOZANO</t>
+          <t>P. SILLA TEBAR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4445</v>
+        <v>-2.3504</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7168</v>
+        <v>-3.3097</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7278</v>
+        <v>0.9594</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5012</v>
+        <v>-3.9319</v>
       </c>
       <c r="H10" t="n">
-        <v>1.5425</v>
+        <v>-3.661</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0413</v>
+        <v>-0.2709</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4801</v>
+        <v>-2.6738</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0886</v>
+        <v>-2.1647</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6084000000000001</v>
+        <v>-0.5091</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0211</v>
+        <v>-1.258</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4539</v>
+        <v>-1.4963</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4329</v>
+        <v>0.2383</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.7548</v>
+        <v>0.3774</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.887</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1322</v>
+        <v>2.2644</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5637</v>
+        <v>0.9023</v>
       </c>
       <c r="T10" t="n">
-        <v>1.0299</v>
+        <v>0.9493</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5338000000000001</v>
+        <v>-0.047</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.7546</v>
+        <v>0.3018</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.3398</v>
+        <v>0.3018</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.4148</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. SILLA TEBAR</t>
+          <t>V. PELUFO LOZANO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5003</v>
+        <v>-2.8691</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.4861</v>
+        <v>-1.0091</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9858</v>
+        <v>-1.86</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.9319</v>
+        <v>0.5012</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.661</v>
+        <v>1.5425</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2709</v>
+        <v>-1.0413</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.6738</v>
+        <v>0.4801</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.1647</v>
+        <v>1.0886</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5091</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.258</v>
+        <v>0.0211</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.4963</v>
+        <v>0.4539</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2383</v>
+        <v>-0.4329</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3774</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.887</v>
       </c>
       <c r="R11" t="n">
-        <v>2.2644</v>
+        <v>1.1322</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7524</v>
+        <v>1.1391</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7729</v>
+        <v>0.7376</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0205</v>
+        <v>0.4015</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3018</v>
+        <v>-3.7546</v>
       </c>
       <c r="W11" t="n">
-        <v>0.3018</v>
+        <v>-0.3398</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-3.4148</v>
       </c>
     </row>
     <row r="12">
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>20.4657</v>
+        <v>21.4449</v>
       </c>
       <c r="E12" t="n">
-        <v>3.1149</v>
+        <v>4.0943</v>
       </c>
       <c r="F12" t="n">
-        <v>17.3508</v>
+        <v>17.3509</v>
       </c>
       <c r="G12" t="n">
-        <v>4.5738</v>
+        <v>4.573799999999999</v>
       </c>
       <c r="H12" t="n">
         <v>-2.0269</v>
@@ -1390,13 +1390,13 @@
         <v>27.3615</v>
       </c>
       <c r="S12" t="n">
-        <v>7.0981</v>
+        <v>8.077200000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>4.9459</v>
+        <v>5.9252</v>
       </c>
       <c r="U12" t="n">
-        <v>2.152</v>
+        <v>2.1519</v>
       </c>
       <c r="V12" t="n">
         <v>-5.3586</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R. DIAZ GALIAN</t>
+          <t>H. RIVAS OSETE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.481</v>
+        <v>1.8713</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2054</v>
+        <v>0.7462</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2756</v>
+        <v>1.1251</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.4886</v>
+        <v>0.6511</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.7115</v>
+        <v>0.5017</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.7771</v>
+        <v>0.1495</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.3669</v>
+        <v>0.7383999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.109</v>
+        <v>0.6973</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.258</v>
+        <v>0.0411</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.1217</v>
+        <v>-0.0873</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6026</v>
+        <v>-0.1956</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.5191</v>
+        <v>0.1083</v>
       </c>
       <c r="P13" t="n">
-        <v>1.6983</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.3774</v>
+        <v>-0.9435</v>
       </c>
       <c r="R13" t="n">
-        <v>2.0757</v>
+        <v>0.3774</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1394</v>
+        <v>-0.1005</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1575</v>
+        <v>-0.2939</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0181</v>
+        <v>0.1934</v>
       </c>
       <c r="V13" t="n">
-        <v>3.132</v>
+        <v>1.8868</v>
       </c>
       <c r="W13" t="n">
-        <v>2.7922</v>
+        <v>1.2452</v>
       </c>
       <c r="X13" t="n">
-        <v>0.3398</v>
+        <v>0.6415999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>H. RIVAS OSETE</t>
+          <t>R. DIAZ GALIAN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4527</v>
+        <v>1.1515</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7462</v>
+        <v>0.0105</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7066</v>
+        <v>1.141</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6511</v>
+        <v>-3.4886</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5017</v>
+        <v>-1.7115</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1495</v>
+        <v>-1.7771</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7383999999999999</v>
+        <v>-2.3669</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6973</v>
+        <v>-1.109</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0411</v>
+        <v>-1.258</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.0873</v>
+        <v>-1.1217</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1956</v>
+        <v>-0.6026</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1083</v>
+        <v>-0.5191</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.5661</v>
+        <v>1.6983</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9435</v>
+        <v>-0.3774</v>
       </c>
       <c r="R14" t="n">
-        <v>0.3774</v>
+        <v>2.0757</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5191</v>
+        <v>-0.1901</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2939</v>
+        <v>-0.0374</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2251</v>
+        <v>-0.1528</v>
       </c>
       <c r="V14" t="n">
-        <v>1.8868</v>
+        <v>3.132</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2452</v>
+        <v>2.7922</v>
       </c>
       <c r="X14" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.3398</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5658</v>
+        <v>0.4851</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2464</v>
+        <v>0.5644</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6807</v>
+        <v>-0.0793</v>
       </c>
       <c r="G15" t="n">
         <v>0.6307</v>
@@ -1624,13 +1624,13 @@
         <v>0.7548</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1405</v>
+        <v>-0.2212</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8999</v>
+        <v>0.2179</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.0405</v>
+        <v>-0.4391</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3018</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.4289</v>
+        <v>-1.8949</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.3462</v>
+        <v>-1.1514</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.0827</v>
+        <v>-0.7435</v>
       </c>
       <c r="G17" t="n">
         <v>0.4864</v>
@@ -1780,13 +1780,13 @@
         <v>0.7548</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2927</v>
+        <v>-0.7586000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2352</v>
+        <v>-0.0403</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.0575</v>
+        <v>-0.7183</v>
       </c>
       <c r="V17" t="n">
         <v>-1.2452</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.7918</v>
+        <v>-2.0328</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.6367</v>
+        <v>-2.3444</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1551</v>
+        <v>0.3117</v>
       </c>
       <c r="G18" t="n">
         <v>-2.1062</v>
@@ -1858,13 +1858,13 @@
         <v>1.887</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8176</v>
+        <v>-0.0586</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8448</v>
+        <v>-0.5525</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0272</v>
+        <v>0.4939</v>
       </c>
       <c r="V18" t="n">
         <v>0.3208</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.0144</v>
+        <v>-2.1207</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6567</v>
+        <v>-0.3644</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.3577</v>
+        <v>-1.7563</v>
       </c>
       <c r="G19" t="n">
         <v>0.2094</v>
@@ -1936,13 +1936,13 @@
         <v>1.5096</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3932</v>
+        <v>-0.4995</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.622</v>
+        <v>-0.3297</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7712</v>
+        <v>-0.1698</v>
       </c>
       <c r="V19" t="n">
         <v>1.566</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.1389</v>
+        <v>-2.2717</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7953</v>
+        <v>-1.8928</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3436</v>
+        <v>-0.3789</v>
       </c>
       <c r="G20" t="n">
         <v>2.76</v>
@@ -2014,13 +2014,13 @@
         <v>2.4531</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.5777</v>
+        <v>-0.7105</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3252</v>
+        <v>-0.4226</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.2526</v>
+        <v>-0.2879</v>
       </c>
       <c r="V20" t="n">
         <v>0.019</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.5842</v>
+        <v>-3.24</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.6495</v>
+        <v>-3.4547</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0653</v>
+        <v>0.2146</v>
       </c>
       <c r="G21" t="n">
         <v>-0.8515</v>
@@ -2092,13 +2092,13 @@
         <v>1.887</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5249</v>
+        <v>-0.1807</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7396</v>
+        <v>-0.5447</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2147</v>
+        <v>0.364</v>
       </c>
       <c r="V21" t="n">
         <v>-0.3208</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-9.324</v>
+        <v>-8.8332</v>
       </c>
       <c r="E22" t="n">
         <v>-9.7812</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4572</v>
+        <v>0.9481000000000001</v>
       </c>
       <c r="G22" t="n">
         <v>-3.1819</v>
@@ -2170,13 +2170,13 @@
         <v>1.5096</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9717</v>
+        <v>-0.4808</v>
       </c>
       <c r="T22" t="n">
         <v>-0.1488</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8229</v>
+        <v>-0.332</v>
       </c>
       <c r="V22" t="n">
         <v>0.3018</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-20.4657</v>
+        <v>-16.5684</v>
       </c>
       <c r="E23" t="n">
-        <v>-17.3506</v>
+        <v>-17.3508</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.1151</v>
+        <v>0.7824999999999998</v>
       </c>
       <c r="G23" t="n">
         <v>-4.573600000000001</v>
@@ -2248,13 +2248,13 @@
         <v>13.209</v>
       </c>
       <c r="S23" t="n">
-        <v>-7.098000000000001</v>
+        <v>-3.2005</v>
       </c>
       <c r="T23" t="n">
-        <v>-2.1521</v>
+        <v>-2.152</v>
       </c>
       <c r="U23" t="n">
-        <v>-4.946</v>
+        <v>-1.0486</v>
       </c>
       <c r="V23" t="n">
         <v>5.3586</v>
